--- a/consent_forms/036_youth_sports_concussion_consent_form--consent_forms.xlsx
+++ b/consent_forms/036_youth_sports_concussion_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Concussion Information</t>
+          <t>Concussion Concussion Info</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Concussion Form</t>
+          <t>Concussion Concussion Form</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>concussion_concussion_symptoms_info</t>
+          <t>concussion_concussion_symptoms_info_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Symptoms Info</t>
+          <t>Concussion Concussion Symptoms Info 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Form Submitted</t>
+          <t>Concussion Concussion Form Submitted</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>concussion_safety_plan</t>
+          <t>concussion_safety_plan_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Safety Plan</t>
+          <t>Concussion Safety Plan 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>concussion_concussion_symptoms_info_choices</t>
+          <t>concussion_concussion_symptoms_info_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>concussion_concussion_symptoms_info_choices</t>
+          <t>concussion_concussion_symptoms_info_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>concussion_safety_plan_choices</t>
+          <t>concussion_safety_plan_3_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>concussion_safety_plan_choices</t>
+          <t>concussion_safety_plan_3_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
